--- a/05_Benchmark_Exemple.xlsx
+++ b/05_Benchmark_Exemple.xlsx
@@ -1221,7 +1221,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>N i B: Lambda, Laia</t>
+          <t>N i B: Kappa, Joan</t>
         </is>
       </c>
     </row>
@@ -1297,17 +1297,17 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>N i B: Xi, Oriol</t>
+          <t>N i B: Novell-Nou1, Aina</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Grup 1: Alpha, Anna</t>
+          <t>Grup 1: Zeta, Francesc</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>Grup 1: Epsilon, Elena</t>
+          <t>Grup 1: Delta, David</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -1336,12 +1336,12 @@
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>Grup 2: Beta, Bernat</t>
+          <t>Grup 2: Alpha, Anna</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>Grup 2: Eta, Gabriela</t>
+          <t>Grup 2: Epsilon, Elena</t>
         </is>
       </c>
       <c r="G12" s="6" t="n"/>
@@ -1415,22 +1415,22 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>N i B: Zeta, Francesc</t>
+          <t>N i B: Xi, Oriol</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>Grup 1: Chi, Xavier</t>
+          <t>Grup 1: Beta, Bernat</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>Grup 1: FixRota-Riaza, Laia</t>
+          <t>Grup 1: Eta, Gabriela</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Grup 1: Iota, Irene</t>
+          <t>Grup 1: Gamma, Carla</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
@@ -1446,17 +1446,17 @@
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Grup 2: Delta, David</t>
+          <t>Grup 2: Chi, Xavier</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>Grup 2: Gamma, Carla</t>
+          <t>Grup 2: FixRota-Riaza, Laia</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Grup 2: Kappa, Joan</t>
+          <t>Grup 2: Iota, Irene</t>
         </is>
       </c>
       <c r="H19" s="6" t="n"/>
@@ -1632,12 +1632,12 @@
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Grup 1: Rotador-29, Erik</t>
+          <t>Grup 1: Rotador-27, Cèsar</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>N i B: Special-Arce, Javi</t>
+          <t>N i B: Sigma, Sílvia</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Grup 2: Rotador-30, Fina</t>
+          <t>Grup 2: Rotador-28, Diana</t>
         </is>
       </c>
       <c r="H6" s="6" t="n"/>
@@ -1713,17 +1713,17 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>N i B: Omega, Zeno</t>
+          <t>N i B: Novell-Nou2, Bernat</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Grup 1: Phi, Víctor</t>
+          <t>Grup 1: Omega, Zeno</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>Grup 1: Rotador-25, Aleix</t>
+          <t>Grup 1: Psi, Yolanda</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -1752,12 +1752,12 @@
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>Grup 2: Pi, Queralt</t>
+          <t>Grup 2: Omicron, Pere</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>Grup 2: Rotador-26, Berta</t>
+          <t>Grup 2: Rho, Roger</t>
         </is>
       </c>
       <c r="G12" s="6" t="n"/>
@@ -1821,37 +1821,37 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
+          <t>N i B: Lambda, Laia</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
           <t>N i B: Mu, Marc</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>N i B: Nu, Núria</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>N i B: Omicron, Pere</t>
-        </is>
-      </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>Grup 1: Psi, Yolanda</t>
+          <t>Grup 1: Phi, Víctor</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>Grup 1: Rotador-27, Cèsar</t>
+          <t>Grup 1: Rotador-25, Aleix</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Grup 1: Sigma, Sílvia</t>
+          <t>Grup 1: Rotador-29, Erik</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>N i B: Special-Lush, Olga</t>
+          <t>N i B: Tau, Tomàs</t>
         </is>
       </c>
     </row>
@@ -1862,17 +1862,17 @@
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Grup 2: Rho, Roger</t>
+          <t>Grup 2: Pi, Queralt</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>Grup 2: Rotador-28, Diana</t>
+          <t>Grup 2: Rotador-26, Berta</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Grup 2: Tau, Tomàs</t>
+          <t>Grup 2: Rotador-30, Fina</t>
         </is>
       </c>
       <c r="H19" s="6" t="n"/>
@@ -2048,12 +2048,12 @@
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Grup 1: FixRota-SMontanez, Pere</t>
+          <t>Grup 1: Special-Arce, Javi</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>N i B: Mu, Marc</t>
+          <t>N i B: Lambda, Laia</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Grup 2: Iota, Irene</t>
+          <t>Grup 2: FixRota-SMontanez, Pere</t>
         </is>
       </c>
       <c r="H6" s="6" t="n"/>
@@ -2262,12 +2262,12 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Grup 1: Kappa, Joan</t>
+          <t>Grup 1: Iota, Irene</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>N i B: Nu, Núria</t>
+          <t>N i B: Special-Lush, Olga</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Grup 2: Lambda, Laia</t>
+          <t>Grup 2: Kappa, Joan</t>
         </is>
       </c>
       <c r="H19" s="6" t="n"/>
@@ -2604,12 +2604,12 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>N i B: Omega, Zeno</t>
+          <t>N i B: Mu, Marc</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>N i B: Omicron, Pere</t>
+          <t>N i B: Nu, Núria</t>
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
